--- a/Apr_24/big_quakes.xlsx
+++ b/Apr_24/big_quakes.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>224 km ESE of Attu Station, Alaska</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>62 km SE of Sinabang, Indonesia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
